--- a/Designer/Designer/Resources/invoice_template.xlsx
+++ b/Designer/Designer/Resources/invoice_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dukkha\DEV\accounting-app\AccountingApp\Designer\Designer\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3326D78A-6B0D-4FC6-ABAA-90AD9168D25B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDBC18C5-1DF5-4076-9FEC-0BC293C955EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1520" yWindow="1520" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57495" yWindow="15990" windowWidth="29010" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="請求書" sheetId="1" r:id="rId1"/>
@@ -221,39 +221,46 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -572,22 +579,22 @@
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
     </row>
     <row r="3" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
       <c r="E3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="3" t="s">
         <v>3</v>
       </c>
     </row>
@@ -595,7 +602,7 @@
       <c r="E4" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -603,7 +610,7 @@
       <c r="E5" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -611,13 +618,13 @@
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
@@ -625,157 +632,169 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="3" t="s">
+      <c r="B9" s="2"/>
+      <c r="C9" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="12" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="11"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
+      <c r="A13" s="13"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
+      <c r="A14" s="13"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
+      <c r="A15" s="13"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
+      <c r="A16" s="13"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
+      <c r="A17" s="13"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="11"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
+      <c r="A18" s="13"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="11"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
+      <c r="A19" s="13"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="11"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
+      <c r="A20" s="13"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="11"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
+      <c r="A21" s="13"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="E22" s="11" t="s">
+      <c r="A22" s="16"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="F22" s="13" t="s">
+      <c r="F22" s="15" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="E23" s="11" t="s">
+      <c r="A23" s="16"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F23" s="13" t="s">
+      <c r="F23" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="E24" s="14" t="s">
+      <c r="A24" s="16"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F24" s="15" t="s">
+      <c r="F24" s="18" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="16" t="s">
+      <c r="A26" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" s="17" t="s">
+      <c r="A29" s="5" t="s">
         <v>27</v>
       </c>
     </row>
